--- a/test_data/Treaties WHTRates/Treaties WHTRates_Test_Cases.xlsx
+++ b/test_data/Treaties WHTRates/Treaties WHTRates_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K6"/>
+  <dimension ref="A1:K9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -803,6 +803,186 @@
         </is>
       </c>
     </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>WHTRates_06</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Treaties WHTRates</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking a rate cell's link opens the treaty article modal</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the Austria row's '15.00' Div-Sub. hold rate must open a modal titled 'Treaty between Australia and Austria' showing the actual treaty article (Article 10, Dividends) the rate derives from - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on WHT Rates.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria, column: Div-Sub. hold</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open WHT Rates
+2. Select Australia
+3. Click the Austria row's Div-Sub. hold rate link
+4. Verify the article modal title and content</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected, clicking the Austria row's '15.00' Div-Sub. hold rate must open a modal titled 'Treaty between Australia and Austria' showing the actual treaty article (Article 10, Dividends) the rate derives from - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Clicking the Austria rate link correctly opened the modal ('Treaty between Australia and Austria\nFull DTA').</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The article modal opens with the correct treaty title and underlying article</t>
+        </is>
+      </c>
+      <c r="K7" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>WHTRates_07</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Treaties WHTRates</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>The article modal's PDF export downloads a real, non-empty file</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected, Austria's article modal open.</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia, partner: Austria</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in, open WHT Rates, select Australia
+2. Open the Austria article modal
+3. Click 'PDF' under Export
+4. Verify a real, non-empty PDF download completed</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>PDF export downloaded 'AU_AT__Treaty_Article.pdf' (21238 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] The PDF export downloads a real, non-empty .pdf file with no failure</t>
+        </is>
+      </c>
+      <c r="K8" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>WHTRates_08</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Treaties WHTRates</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>The table-level 'Export as Excel' button downloads the whole table</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected (no rate link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>User is logged in, Australia selected on WHT Rates.</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>Country: Australia</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1. Log in and open WHT Rates
+2. Select Australia
+3. Click the 'Export as Excel' icon button
+4. Verify a real, non-empty .xlsx download completed</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>With Australia selected (no rate link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Table export downloaded 'AU_WHTRates.xlsx' (5017 bytes) successfully.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>[PASS] Exporting the table downloads a real, non-empty .xlsx file with no failure</t>
+        </is>
+      </c>
+      <c r="K9" s="3" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/test_data/Treaties WHTRates/Treaties WHTRates_Test_Cases.xlsx
+++ b/test_data/Treaties WHTRates/Treaties WHTRates_Test_Cases.xlsx
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>WHT Rates loaded correctly at https://regplus.kaz.com.bd/wta/WHTRates.</t>
+          <t>WHT Rates loaded correctly at https://regplusrc.reganalytics.com/wta/WHTRates.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -612,7 +612,7 @@
       </c>
       <c r="I3" s="2" t="inlineStr">
         <is>
-          <t>Selecting Australia rendered the WHT rates table with the expected headers and 44 rows.</t>
+          <t>Selecting Australia rendered the WHT rates table with the expected headers and 46 rows.</t>
         </is>
       </c>
       <c r="J3" s="2" t="inlineStr">
@@ -969,7 +969,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>Table export downloaded 'AU_WHTRates.xlsx' (5017 bytes) successfully.</t>
+          <t>Table export downloaded 'AU_WHTRates.xlsx' (5095 bytes) successfully.</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">

--- a/test_data/Treaties WHTRates/Treaties WHTRates_Test_Cases.xlsx
+++ b/test_data/Treaties WHTRates/Treaties WHTRates_Test_Cases.xlsx
@@ -436,7 +436,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K9"/>
+  <dimension ref="A1:K3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -553,7 +553,7 @@
       </c>
       <c r="I2" s="2" t="inlineStr">
         <is>
-          <t>WHT Rates loaded correctly at https://regplusrc.reganalytics.com/wta/WHTRates.</t>
+          <t>WHT Rates loaded correctly at https://regplus.reganalytics.com/wta/WHTRates.</t>
         </is>
       </c>
       <c r="J2" s="2" t="inlineStr">
@@ -621,363 +621,6 @@
         </is>
       </c>
       <c r="K3" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="2" t="inlineStr">
-        <is>
-          <t>WHTRates_03</t>
-        </is>
-      </c>
-      <c r="B4" s="2" t="inlineStr">
-        <is>
-          <t>Treaties WHTRates</t>
-        </is>
-      </c>
-      <c r="C4" s="2" t="inlineStr">
-        <is>
-          <t>The first table row is always 'Domestic WHT rates' for the selected country</t>
-        </is>
-      </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, the first row of the WHT rates table must be the literal 'Domestic WHT rates' row (the selected country's own domestic rates), not a treaty partner row.</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on WHT Rates.</t>
-        </is>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open WHT Rates
-2. Select Australia
-3. Verify the first table row reads 'Domestic WHT rates'</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, the first row of the WHT rates table must be the literal 'Domestic WHT rates' row (the selected country's own domestic rates), not a treaty partner row.</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>The first row of the WHT rates table correctly reads 'Domestic WHT rates'.</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] First row is 'Domestic WHT rates'</t>
-        </is>
-      </c>
-      <c r="K4" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" s="2" t="inlineStr">
-        <is>
-          <t>WHTRates_04</t>
-        </is>
-      </c>
-      <c r="B5" s="2" t="inlineStr">
-        <is>
-          <t>Treaties WHTRates</t>
-        </is>
-      </c>
-      <c r="C5" s="2" t="inlineStr">
-        <is>
-          <t>The Austria row shows the expected Dividend (Sub-hold) rate</t>
-        </is>
-      </c>
-      <c r="D5" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, the row for 'Austria' must show '15.00' as its Div-Sub. hold rate.</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on WHT Rates.</t>
-        </is>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open WHT Rates
-2. Select Australia
-3. Verify the 'Austria' row contains '15.00'</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, the row for 'Austria' must show '15.00' as its Div-Sub. hold rate.</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>The 'Austria' row correctly shows a '15.00' Div-Sub. hold rate.</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The 'Austria' row contains a '15.00' rate</t>
-        </is>
-      </c>
-      <c r="K5" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" s="2" t="inlineStr">
-        <is>
-          <t>WHTRates_05</t>
-        </is>
-      </c>
-      <c r="B6" s="2" t="inlineStr">
-        <is>
-          <t>Treaties WHTRates</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country shows the 'No countries found' message</t>
-        </is>
-      </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message.</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in and on WHT Rates.</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>Search text: zzzznotarealcountry</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open WHT Rates
-2. Type 'zzzznotarealcountry' into the search box
-3. Verify the 'No countries found' message is shown</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>Typing an unmatched string into 'Search countries' must show the 'No countries found matching ...' message.</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>Searching for a non-existent country correctly showed the 'No countries found' message.</t>
-        </is>
-      </c>
-      <c r="J6" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] 'No countries found matching...' message is shown for an unmatched search</t>
-        </is>
-      </c>
-      <c r="K6" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" s="2" t="inlineStr">
-        <is>
-          <t>WHTRates_06</t>
-        </is>
-      </c>
-      <c r="B7" s="2" t="inlineStr">
-        <is>
-          <t>Treaties WHTRates</t>
-        </is>
-      </c>
-      <c r="C7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking a rate cell's link opens the treaty article modal</t>
-        </is>
-      </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the Austria row's '15.00' Div-Sub. hold rate must open a modal titled 'Treaty between Australia and Austria' showing the actual treaty article (Article 10, Dividends) the rate derives from - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on WHT Rates.</t>
-        </is>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria, column: Div-Sub. hold</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open WHT Rates
-2. Select Australia
-3. Click the Austria row's Div-Sub. hold rate link
-4. Verify the article modal title and content</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected, clicking the Austria row's '15.00' Div-Sub. hold rate must open a modal titled 'Treaty between Australia and Austria' showing the actual treaty article (Article 10, Dividends) the rate derives from - same click-to-modal pattern confirmed on Treaties &gt; Other Articles.</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="inlineStr">
-        <is>
-          <t>Clicking the Austria rate link correctly opened the modal ('Treaty between Australia and Austria\nFull DTA').</t>
-        </is>
-      </c>
-      <c r="J7" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The article modal opens with the correct treaty title and underlying article</t>
-        </is>
-      </c>
-      <c r="K7" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="2" t="inlineStr">
-        <is>
-          <t>WHTRates_07</t>
-        </is>
-      </c>
-      <c r="B8" s="2" t="inlineStr">
-        <is>
-          <t>Treaties WHTRates</t>
-        </is>
-      </c>
-      <c r="C8" s="2" t="inlineStr">
-        <is>
-          <t>The article modal's PDF export downloads a real, non-empty file</t>
-        </is>
-      </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected, Austria's article modal open.</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia, partner: Austria</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in, open WHT Rates, select Australia
-2. Open the Austria article modal
-3. Click 'PDF' under Export
-4. Verify a real, non-empty PDF download completed</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>With the Austria article modal open (Australia selected), clicking 'PDF' under Export must trigger a real file download with no failure and a non-zero size.</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>PDF export downloaded 'AU_AT__Treaty_Article.pdf' (21238 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] The PDF export downloads a real, non-empty .pdf file with no failure</t>
-        </is>
-      </c>
-      <c r="K8" s="3" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" s="2" t="inlineStr">
-        <is>
-          <t>WHTRates_08</t>
-        </is>
-      </c>
-      <c r="B9" s="2" t="inlineStr">
-        <is>
-          <t>Treaties WHTRates</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr">
-        <is>
-          <t>The table-level 'Export as Excel' button downloads the whole table</t>
-        </is>
-      </c>
-      <c r="D9" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected (no rate link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="inlineStr">
-        <is>
-          <t>User is logged in, Australia selected on WHT Rates.</t>
-        </is>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>Country: Australia</t>
-        </is>
-      </c>
-      <c r="G9" s="2" t="inlineStr">
-        <is>
-          <t>1. Log in and open WHT Rates
-2. Select Australia
-3. Click the 'Export as Excel' icon button
-4. Verify a real, non-empty .xlsx download completed</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>With Australia selected (no rate link clicked), clicking the table's 'Export as Excel' icon button must trigger a real, non-empty .xlsx download.</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="inlineStr">
-        <is>
-          <t>Table export downloaded 'AU_WHTRates.xlsx' (5095 bytes) successfully.</t>
-        </is>
-      </c>
-      <c r="J9" s="2" t="inlineStr">
-        <is>
-          <t>[PASS] Exporting the table downloads a real, non-empty .xlsx file with no failure</t>
-        </is>
-      </c>
-      <c r="K9" s="3" t="inlineStr">
         <is>
           <t>PASS</t>
         </is>
